--- a/Outputs/Scenarios/PtX_demand_AT_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_AT_Electrification.xlsx
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>5.507271038521231e-05</v>
+        <v>5.50727103852123e-05</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.0003228682160306722</v>
       </c>
       <c r="K42" t="n">
-        <v>5.507271038521231e-05</v>
+        <v>5.50727103852123e-05</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_AT_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_AT_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.00414387072335156</v>
       </c>
       <c r="K16" t="n">
-        <v>6.050275601471642e-05</v>
+        <v>0.0001385977397442053</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.00837926691194e-05</v>
+        <v>5.939903131894516e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4.033517067647762e-05</v>
+        <v>2.375961252757806e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>6.050275601471642e-05</v>
+        <v>2.375961252757806e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0003320905725630834</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0001109110757891913</v>
+        <v>0.0001088877746795143</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.002010144934382977</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0007929373920657594</v>
+        <v>0.0007784721901564352</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>5.970616272678076e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>1.00837926691194e-05</v>
+        <v>5.939903131894516e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.006134496104582772</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0003304362623112738</v>
+        <v>0.000693916150853675</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>5.50727103852123e-05</v>
+        <v>2.973926360801465e-05</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0002202908415408492</v>
+        <v>0.0001189570544320586</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0003304362623112738</v>
+        <v>0.0001189570544320586</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0003228682160306722</v>
       </c>
       <c r="K42" t="n">
-        <v>5.50727103852123e-05</v>
+        <v>2.973926360801465e-05</v>
       </c>
     </row>
     <row r="43">
